--- a/Orario.xlsx
+++ b/Orario.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentiunical-my.sharepoint.com/personal/roberto_antonucci_servizimicrosoft_unical_it/Documents/Documenti/Documents/DOCUMENTI/Protocollo Informatico/Titolo 3/Titolo III.8/Programmazione Didattica 2026-2027/Orario 1 semestre/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\Display_DESF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{47FFEA90-37AE-410C-B2D2-9CE352867A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C8742A-9CEA-489E-952C-A163C63CE582}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57F6A8C-9B5D-4C83-92FF-1DA3679E2842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Economia I" sheetId="1" r:id="rId1"/>
@@ -300,9 +300,6 @@
     <t>Diritto delle autonomie territoriali</t>
   </si>
   <si>
-    <t>U. Adamo - da definire</t>
-  </si>
-  <si>
     <t>Lingua Inglese (avanzato)</t>
   </si>
   <si>
@@ -459,6 +456,9 @@
   </si>
   <si>
     <t>3° anno - Periodo settimanale: 05 – 10 ott 2026</t>
+  </si>
+  <si>
+    <t>U. Adamo - F. Puzzo</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1527,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -2477,7 +2477,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -2566,19 +2566,19 @@
       <c r="B9" s="26"/>
       <c r="C9" s="22"/>
       <c r="D9" s="62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="62" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="20"/>
@@ -2610,19 +2610,19 @@
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="45"/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="71" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="20"/>
@@ -2688,19 +2688,19 @@
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
       <c r="D15" s="29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="20"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="39" t="s">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="45"/>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="82" t="s">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="45"/>
@@ -2862,7 +2862,7 @@
       <c r="B25" s="26"/>
       <c r="C25" s="14"/>
       <c r="D25" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="34" t="s">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="45"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="25"/>
@@ -3148,7 +3148,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -3233,11 +3233,11 @@
       <c r="B9" s="26"/>
       <c r="C9" s="22"/>
       <c r="D9" s="62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="20"/>
@@ -3269,11 +3269,11 @@
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="45"/>
@@ -3339,15 +3339,15 @@
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
       <c r="D15" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="63" t="s">
@@ -3383,19 +3383,19 @@
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="25"/>
@@ -3540,15 +3540,15 @@
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="69" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="25"/>
@@ -3809,7 +3809,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -3896,11 +3896,11 @@
       <c r="D9" s="20"/>
       <c r="E9" s="28"/>
       <c r="F9" s="62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="20"/>
@@ -3932,11 +3932,11 @@
       <c r="D11" s="45"/>
       <c r="E11" s="19"/>
       <c r="F11" s="68" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="68" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="45"/>
@@ -3998,11 +3998,11 @@
       <c r="D15" s="20"/>
       <c r="E15" s="28"/>
       <c r="F15" s="63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="63" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="25"/>
@@ -4034,11 +4034,11 @@
       <c r="D17" s="45"/>
       <c r="E17" s="28"/>
       <c r="F17" s="69" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="69" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="25"/>
@@ -4141,11 +4141,11 @@
       <c r="D24" s="20"/>
       <c r="E24" s="19"/>
       <c r="F24" s="85" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="85" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
@@ -4177,11 +4177,11 @@
       <c r="D26" s="45"/>
       <c r="E26" s="19"/>
       <c r="F26" s="87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="45"/>
@@ -4457,7 +4457,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -4606,21 +4606,21 @@
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="55"/>
       <c r="G11" s="19"/>
       <c r="H11" s="39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="2:18" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -5193,7 +5193,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -5332,19 +5332,19 @@
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="80" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="49" t="s">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="80" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="45"/>
@@ -5865,7 +5865,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -6526,7 +6526,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -6661,7 +6661,7 @@
       <c r="D11" s="45"/>
       <c r="E11" s="19"/>
       <c r="F11" s="80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="39" t="s">
@@ -6669,11 +6669,11 @@
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -6787,15 +6787,15 @@
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="49" t="s">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="45"/>
@@ -7217,7 +7217,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -7888,7 +7888,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -7983,11 +7983,11 @@
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="62" t="s">
@@ -8027,23 +8027,23 @@
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="68" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="68" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="68" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8109,19 +8109,19 @@
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
       <c r="D15" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="20"/>
@@ -8153,19 +8153,19 @@
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="45"/>
@@ -8268,11 +8268,11 @@
       <c r="B24" s="32"/>
       <c r="C24" s="14"/>
       <c r="D24" s="85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="76"/>
@@ -8304,11 +8304,11 @@
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="76"/>
@@ -8569,7 +8569,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -8660,23 +8660,23 @@
       <c r="B9" s="26"/>
       <c r="C9" s="22"/>
       <c r="D9" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="97" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="97" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8712,19 +8712,19 @@
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8792,23 +8792,23 @@
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
       <c r="D15" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8840,23 +8840,23 @@
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="94" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="94" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="91" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="82" t="s">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="92" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="25"/>
@@ -9007,19 +9007,19 @@
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="94" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="25"/>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="91" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="25"/>
@@ -9083,15 +9083,15 @@
       <c r="B30" s="32"/>
       <c r="C30" s="19"/>
       <c r="D30" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G30" s="19"/>
       <c r="H30" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I30" s="19"/>
       <c r="J30" s="25"/>
@@ -9122,7 +9122,7 @@
         <v>0.70833333333333304</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E32" s="52"/>
       <c r="F32" s="39" t="s">
@@ -9310,7 +9310,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -9399,15 +9399,15 @@
       <c r="D9" s="20"/>
       <c r="E9" s="28"/>
       <c r="F9" s="97" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="97" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="20"/>
@@ -9439,15 +9439,15 @@
       <c r="D11" s="20"/>
       <c r="E11" s="19"/>
       <c r="F11" s="99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="45"/>
@@ -9511,11 +9511,11 @@
       <c r="F15" s="20"/>
       <c r="G15" s="19"/>
       <c r="H15" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="20"/>
@@ -9547,11 +9547,11 @@
       <c r="F17" s="20"/>
       <c r="G17" s="19"/>
       <c r="H17" s="68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="45"/>
@@ -9652,11 +9652,11 @@
       <c r="D24" s="20"/>
       <c r="E24" s="19"/>
       <c r="F24" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
@@ -9688,11 +9688,11 @@
       <c r="D26" s="45"/>
       <c r="E26" s="19"/>
       <c r="F26" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="45"/>
@@ -9705,11 +9705,11 @@
       <c r="D27" s="45"/>
       <c r="E27" s="19"/>
       <c r="F27" s="101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G27" s="19"/>
       <c r="H27" s="101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I27" s="19"/>
       <c r="J27" s="25"/>

--- a/Orario.xlsx
+++ b/Orario.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\Display_DESF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentiunical-my.sharepoint.com/personal/roberto_antonucci_servizimicrosoft_unical_it/Documents/Documenti/Documents/DOCUMENTI/Protocollo Informatico/Titolo 3/Titolo III.8/Programmazione Didattica 2026-2027/Orario 1 semestre/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57F6A8C-9B5D-4C83-92FF-1DA3679E2842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{C52FFF61-9DFA-42D2-97D1-8098F82D12C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F612F13F-AC7F-47F0-8DE2-3A0BFFEFC53F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Economia I" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="126">
   <si>
     <t>Lunedì</t>
   </si>
@@ -300,6 +300,9 @@
     <t>Diritto delle autonomie territoriali</t>
   </si>
   <si>
+    <t>U. Adamo - da definire</t>
+  </si>
+  <si>
     <t>Lingua Inglese (avanzato)</t>
   </si>
   <si>
@@ -361,9 +364,6 @@
   </si>
   <si>
     <t xml:space="preserve">M. Stranges </t>
-  </si>
-  <si>
-    <t>nota: inizia il 6 ottobre</t>
   </si>
   <si>
     <t>Business intelligence e Big data analytics modulo a) Business intelligence</t>
@@ -443,22 +443,19 @@
     <t>L. Errico</t>
   </si>
   <si>
-    <t>Aula Informatica 2 (Cubo 3C - DiScAG)</t>
-  </si>
-  <si>
     <t>Laboratorio didattico Informatica 1 (Cubo 3C - DiScAG)</t>
   </si>
   <si>
-    <t>1° anno - Periodo settimanale: 05 – 10 ott 2026</t>
-  </si>
-  <si>
-    <t>2° anno - Periodo settimanale: 05 – 10 ott 2026</t>
-  </si>
-  <si>
-    <t>3° anno - Periodo settimanale: 05 – 10 ott 2026</t>
-  </si>
-  <si>
-    <t>U. Adamo - F. Puzzo</t>
+    <t>1° anno - Periodo settimanale: 12 – 17 ott 2026</t>
+  </si>
+  <si>
+    <t>2° anno - Periodo settimanale: 12 – 17 ott 2026</t>
+  </si>
+  <si>
+    <t>3° anno - Periodo settimanale: 12 – 17 ott 2026</t>
+  </si>
+  <si>
+    <t>Auletta Seminari (Cubo 1C)</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1524,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -1618,9 +1615,7 @@
         <v>0.375</v>
       </c>
       <c r="C8" s="22"/>
-      <c r="D8" s="24" t="s">
-        <v>10</v>
-      </c>
+      <c r="D8" s="90"/>
       <c r="E8" s="14"/>
       <c r="F8" s="24" t="s">
         <v>10</v>
@@ -1649,9 +1644,7 @@
     <row r="9" spans="2:18" s="11" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B9" s="26"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="29" t="s">
-        <v>39</v>
-      </c>
+      <c r="D9" s="90"/>
       <c r="E9" s="19"/>
       <c r="F9" s="29" t="s">
         <v>39</v>
@@ -1680,9 +1673,7 @@
     <row r="10" spans="2:18" s="11" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B10" s="32"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="34" t="s">
-        <v>17</v>
-      </c>
+      <c r="D10" s="90"/>
       <c r="E10" s="28"/>
       <c r="F10" s="34" t="s">
         <v>17</v>
@@ -1713,9 +1704,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C11" s="14"/>
-      <c r="D11" s="38" t="s">
-        <v>35</v>
-      </c>
+      <c r="D11" s="90"/>
       <c r="E11" s="19"/>
       <c r="F11" s="38" t="s">
         <v>40</v>
@@ -1744,9 +1733,7 @@
     <row r="12" spans="2:18" s="11" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B12" s="41"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="42" t="s">
-        <v>14</v>
-      </c>
+      <c r="D12" s="90"/>
       <c r="E12" s="19"/>
       <c r="F12" s="42" t="s">
         <v>15</v>
@@ -1775,9 +1762,7 @@
     <row r="13" spans="2:18" s="11" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B13" s="41"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="42" t="s">
-        <v>9</v>
-      </c>
+      <c r="D13" s="90"/>
       <c r="E13" s="19"/>
       <c r="F13" s="42" t="s">
         <v>31</v>
@@ -2477,7 +2462,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -2648,11 +2633,11 @@
       </c>
       <c r="E13" s="19"/>
       <c r="F13" s="71" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="71" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="71" t="s">
@@ -2691,12 +2676,12 @@
         <v>99</v>
       </c>
       <c r="E15" s="28"/>
-      <c r="F15" s="30" t="s">
+      <c r="F15" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="30" t="s">
         <v>101</v>
-      </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="47" t="s">
-        <v>103</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="29" t="s">
@@ -2712,11 +2697,11 @@
         <v>17</v>
       </c>
       <c r="E16" s="28"/>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="48" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="19"/>
-      <c r="H16" s="48" t="s">
+      <c r="H16" s="35" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="28"/>
@@ -2735,11 +2720,11 @@
         <v>100</v>
       </c>
       <c r="E17" s="28"/>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="49" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="19"/>
-      <c r="H17" s="49" t="s">
+      <c r="H17" s="39" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="19"/>
@@ -2754,9 +2739,9 @@
       <c r="C18" s="14"/>
       <c r="D18" s="34"/>
       <c r="E18" s="19"/>
-      <c r="F18" s="35"/>
+      <c r="F18" s="48"/>
       <c r="G18" s="19"/>
-      <c r="H18" s="48"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="19"/>
       <c r="J18" s="34"/>
       <c r="K18" s="19"/>
@@ -2769,12 +2754,12 @@
         <v>24</v>
       </c>
       <c r="E19" s="19"/>
-      <c r="F19" s="43" t="s">
+      <c r="F19" s="75" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="19"/>
-      <c r="H19" s="75" t="s">
-        <v>121</v>
+      <c r="H19" s="43" t="s">
+        <v>125</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="82" t="s">
@@ -3148,7 +3133,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -3809,7 +3794,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -4457,7 +4442,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -5193,7 +5178,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -5392,11 +5377,11 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C14" s="22"/>
-      <c r="D14" s="20"/>
+      <c r="D14" s="24" t="s">
+        <v>11</v>
+      </c>
       <c r="E14" s="14"/>
-      <c r="F14" s="24" t="s">
-        <v>11</v>
-      </c>
+      <c r="F14" s="20"/>
       <c r="G14" s="19"/>
       <c r="H14" s="24" t="s">
         <v>11</v>
@@ -5411,11 +5396,11 @@
     <row r="15" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="20"/>
+      <c r="D15" s="47" t="s">
+        <v>26</v>
+      </c>
       <c r="E15" s="28"/>
-      <c r="F15" s="47" t="s">
-        <v>26</v>
-      </c>
+      <c r="F15" s="20"/>
       <c r="G15" s="19"/>
       <c r="H15" s="29" t="s">
         <v>55</v>
@@ -5430,11 +5415,11 @@
     <row r="16" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B16" s="32"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="20"/>
+      <c r="D16" s="48" t="s">
+        <v>17</v>
+      </c>
       <c r="E16" s="28"/>
-      <c r="F16" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="F16" s="20"/>
       <c r="G16" s="19"/>
       <c r="H16" s="34" t="s">
         <v>17</v>
@@ -5451,11 +5436,11 @@
         <v>0.5</v>
       </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="20"/>
+      <c r="D17" s="49" t="s">
+        <v>54</v>
+      </c>
       <c r="E17" s="28"/>
-      <c r="F17" s="49" t="s">
-        <v>54</v>
-      </c>
+      <c r="F17" s="20"/>
       <c r="G17" s="19"/>
       <c r="H17" s="38" t="s">
         <v>56</v>
@@ -5470,9 +5455,9 @@
     <row r="18" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B18" s="41"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="20"/>
+      <c r="D18" s="49"/>
       <c r="E18" s="19"/>
-      <c r="F18" s="49"/>
+      <c r="F18" s="20"/>
       <c r="G18" s="19"/>
       <c r="H18" s="34"/>
       <c r="I18" s="19"/>
@@ -5483,11 +5468,11 @@
     <row r="19" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B19" s="32"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="20"/>
+      <c r="D19" s="75" t="s">
+        <v>32</v>
+      </c>
       <c r="E19" s="19"/>
-      <c r="F19" s="75" t="s">
-        <v>32</v>
-      </c>
+      <c r="F19" s="20"/>
       <c r="G19" s="19"/>
       <c r="H19" s="82" t="s">
         <v>32</v>
@@ -5865,7 +5850,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -6289,7 +6274,7 @@
       <c r="K27" s="19"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="2:12" s="51" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B28" s="32"/>
       <c r="C28" s="14"/>
       <c r="D28" s="20"/>
@@ -6297,7 +6282,7 @@
       <c r="F28" s="20"/>
       <c r="G28" s="19"/>
       <c r="H28" s="75" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="55"/>
@@ -6526,7 +6511,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -7217,7 +7202,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -7888,7 +7873,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -7983,11 +7968,11 @@
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="62" t="s">
@@ -8027,23 +8012,23 @@
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="68" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="68" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="68" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8109,19 +8094,19 @@
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
       <c r="D15" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="20"/>
@@ -8153,19 +8138,19 @@
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="45"/>
@@ -8268,11 +8253,11 @@
       <c r="B24" s="32"/>
       <c r="C24" s="14"/>
       <c r="D24" s="85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="76"/>
@@ -8304,11 +8289,11 @@
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="76"/>
@@ -8569,7 +8554,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -8660,23 +8645,23 @@
       <c r="B9" s="26"/>
       <c r="C9" s="22"/>
       <c r="D9" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" s="28"/>
       <c r="F9" s="97" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="97" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8712,19 +8697,19 @@
       </c>
       <c r="E11" s="19"/>
       <c r="F11" s="99" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="99" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8792,23 +8777,23 @@
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
       <c r="D15" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" s="28"/>
       <c r="F15" s="47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="92" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="92" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8840,23 +8825,23 @@
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" s="28"/>
       <c r="F17" s="49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="94" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I17" s="19"/>
       <c r="J17" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="94" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
@@ -8880,11 +8865,11 @@
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="75" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="82" t="s">
@@ -8975,7 +8960,7 @@
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="92" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" s="19"/>
       <c r="L24" s="25"/>
@@ -9007,19 +8992,19 @@
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E26" s="19"/>
       <c r="F26" s="87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="87" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="94" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" s="19"/>
       <c r="L26" s="25"/>
@@ -9053,7 +9038,7 @@
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="25"/>
@@ -9083,15 +9068,15 @@
       <c r="B30" s="32"/>
       <c r="C30" s="19"/>
       <c r="D30" s="47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E30" s="19"/>
       <c r="F30" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" s="19"/>
       <c r="H30" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I30" s="19"/>
       <c r="J30" s="25"/>
@@ -9122,7 +9107,7 @@
         <v>0.70833333333333304</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E32" s="52"/>
       <c r="F32" s="39" t="s">
@@ -9310,7 +9295,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -9399,15 +9384,15 @@
       <c r="D9" s="20"/>
       <c r="E9" s="28"/>
       <c r="F9" s="97" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" s="19"/>
       <c r="H9" s="97" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I9" s="19"/>
       <c r="J9" s="85" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="20"/>
@@ -9439,15 +9424,15 @@
       <c r="D11" s="20"/>
       <c r="E11" s="19"/>
       <c r="F11" s="99" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="99" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I11" s="19"/>
       <c r="J11" s="87" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="45"/>
@@ -9493,9 +9478,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="20"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="24" t="s">
-        <v>11</v>
-      </c>
+      <c r="H14" s="25"/>
       <c r="I14" s="14"/>
       <c r="J14" s="24" t="s">
         <v>11</v>
@@ -9510,12 +9493,10 @@
       <c r="E15" s="28"/>
       <c r="F15" s="20"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="62" t="s">
-        <v>93</v>
-      </c>
+      <c r="H15" s="25"/>
       <c r="I15" s="19"/>
       <c r="J15" s="62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="20"/>
@@ -9527,9 +9508,7 @@
       <c r="E16" s="28"/>
       <c r="F16" s="20"/>
       <c r="G16" s="19"/>
-      <c r="H16" s="65" t="s">
-        <v>17</v>
-      </c>
+      <c r="H16" s="25"/>
       <c r="I16" s="28"/>
       <c r="J16" s="65" t="s">
         <v>17</v>
@@ -9546,12 +9525,10 @@
       <c r="E17" s="28"/>
       <c r="F17" s="20"/>
       <c r="G17" s="19"/>
-      <c r="H17" s="68" t="s">
-        <v>94</v>
-      </c>
+      <c r="H17" s="25"/>
       <c r="I17" s="19"/>
       <c r="J17" s="68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="45"/>
@@ -9563,7 +9540,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="19"/>
-      <c r="H18" s="65"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="19"/>
       <c r="J18" s="65"/>
       <c r="K18" s="19"/>
@@ -9576,9 +9553,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="71" t="s">
-        <v>24</v>
-      </c>
+      <c r="H19" s="25"/>
       <c r="I19" s="19"/>
       <c r="J19" s="71" t="s">
         <v>24</v>
@@ -9652,11 +9627,11 @@
       <c r="D24" s="20"/>
       <c r="E24" s="19"/>
       <c r="F24" s="47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="47" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
@@ -9688,11 +9663,11 @@
       <c r="D26" s="45"/>
       <c r="E26" s="19"/>
       <c r="F26" s="49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I26" s="19"/>
       <c r="J26" s="45"/>
@@ -9704,13 +9679,9 @@
       <c r="C27" s="14"/>
       <c r="D27" s="45"/>
       <c r="E27" s="19"/>
-      <c r="F27" s="101" t="s">
-        <v>95</v>
-      </c>
+      <c r="F27" s="101"/>
       <c r="G27" s="19"/>
-      <c r="H27" s="101" t="s">
-        <v>95</v>
-      </c>
+      <c r="H27" s="101"/>
       <c r="I27" s="19"/>
       <c r="J27" s="25"/>
       <c r="K27" s="19"/>

--- a/Orario.xlsx
+++ b/Orario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentiunical-my.sharepoint.com/personal/roberto_antonucci_servizimicrosoft_unical_it/Documents/Documenti/Documents/DOCUMENTI/Protocollo Informatico/Titolo 3/Titolo III.8/Programmazione Didattica 2026-2027/Orario 1 semestre/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{C52FFF61-9DFA-42D2-97D1-8098F82D12C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F612F13F-AC7F-47F0-8DE2-3A0BFFEFC53F}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{47FFEA90-37AE-410C-B2D2-9CE352867A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C1434F-C354-45CA-BCBB-F197073231B4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Economia I" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="126">
   <si>
     <t>Lunedì</t>
   </si>
@@ -443,19 +443,19 @@
     <t>L. Errico</t>
   </si>
   <si>
+    <t>Aula Informatica 2 (Cubo 3C - DiScAG)</t>
+  </si>
+  <si>
     <t>Laboratorio didattico Informatica 1 (Cubo 3C - DiScAG)</t>
   </si>
   <si>
-    <t>1° anno - Periodo settimanale: 12 – 17 ott 2026</t>
-  </si>
-  <si>
-    <t>2° anno - Periodo settimanale: 12 – 17 ott 2026</t>
-  </si>
-  <si>
-    <t>3° anno - Periodo settimanale: 12 – 17 ott 2026</t>
-  </si>
-  <si>
-    <t>Auletta Seminari (Cubo 1C)</t>
+    <t>1° anno - Periodo settimanale: 05 – 10 ott 2026</t>
+  </si>
+  <si>
+    <t>2° anno - Periodo settimanale: 05 – 10 ott 2026</t>
+  </si>
+  <si>
+    <t>3° anno - Periodo settimanale: 05 – 10 ott 2026</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1524,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -1615,7 +1615,9 @@
         <v>0.375</v>
       </c>
       <c r="C8" s="22"/>
-      <c r="D8" s="90"/>
+      <c r="D8" s="24" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="24" t="s">
         <v>10</v>
@@ -1644,7 +1646,9 @@
     <row r="9" spans="2:18" s="11" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
       <c r="B9" s="26"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="90"/>
+      <c r="D9" s="29" t="s">
+        <v>39</v>
+      </c>
       <c r="E9" s="19"/>
       <c r="F9" s="29" t="s">
         <v>39</v>
@@ -1673,7 +1677,9 @@
     <row r="10" spans="2:18" s="11" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B10" s="32"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="90"/>
+      <c r="D10" s="34" t="s">
+        <v>17</v>
+      </c>
       <c r="E10" s="28"/>
       <c r="F10" s="34" t="s">
         <v>17</v>
@@ -1704,7 +1710,9 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C11" s="14"/>
-      <c r="D11" s="90"/>
+      <c r="D11" s="38" t="s">
+        <v>35</v>
+      </c>
       <c r="E11" s="19"/>
       <c r="F11" s="38" t="s">
         <v>40</v>
@@ -1733,7 +1741,9 @@
     <row r="12" spans="2:18" s="11" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B12" s="41"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="90"/>
+      <c r="D12" s="42" t="s">
+        <v>14</v>
+      </c>
       <c r="E12" s="19"/>
       <c r="F12" s="42" t="s">
         <v>15</v>
@@ -1762,7 +1772,9 @@
     <row r="13" spans="2:18" s="11" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B13" s="41"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="90"/>
+      <c r="D13" s="42" t="s">
+        <v>9</v>
+      </c>
       <c r="E13" s="19"/>
       <c r="F13" s="42" t="s">
         <v>31</v>
@@ -2462,7 +2474,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -2633,11 +2645,11 @@
       </c>
       <c r="E13" s="19"/>
       <c r="F13" s="71" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="71" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="I13" s="19"/>
       <c r="J13" s="71" t="s">
@@ -2676,12 +2688,12 @@
         <v>99</v>
       </c>
       <c r="E15" s="28"/>
-      <c r="F15" s="47" t="s">
+      <c r="F15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="H15" s="47" t="s">
         <v>103</v>
-      </c>
-      <c r="G15" s="19"/>
-      <c r="H15" s="30" t="s">
-        <v>101</v>
       </c>
       <c r="I15" s="19"/>
       <c r="J15" s="29" t="s">
@@ -2697,11 +2709,11 @@
         <v>17</v>
       </c>
       <c r="E16" s="28"/>
-      <c r="F16" s="48" t="s">
+      <c r="F16" s="35" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="19"/>
-      <c r="H16" s="35" t="s">
+      <c r="H16" s="48" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="28"/>
@@ -2720,11 +2732,11 @@
         <v>100</v>
       </c>
       <c r="E17" s="28"/>
-      <c r="F17" s="49" t="s">
+      <c r="F17" s="39" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="19"/>
-      <c r="H17" s="39" t="s">
+      <c r="H17" s="49" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="19"/>
@@ -2739,9 +2751,9 @@
       <c r="C18" s="14"/>
       <c r="D18" s="34"/>
       <c r="E18" s="19"/>
-      <c r="F18" s="48"/>
+      <c r="F18" s="35"/>
       <c r="G18" s="19"/>
-      <c r="H18" s="35"/>
+      <c r="H18" s="48"/>
       <c r="I18" s="19"/>
       <c r="J18" s="34"/>
       <c r="K18" s="19"/>
@@ -2754,12 +2766,12 @@
         <v>24</v>
       </c>
       <c r="E19" s="19"/>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="43" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="19"/>
-      <c r="H19" s="43" t="s">
-        <v>125</v>
+      <c r="H19" s="75" t="s">
+        <v>121</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="82" t="s">
@@ -2816,9 +2828,7 @@
       <c r="C23" s="14"/>
       <c r="D23" s="74"/>
       <c r="E23" s="19"/>
-      <c r="F23" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="F23" s="25"/>
       <c r="G23" s="19"/>
       <c r="H23" s="74"/>
       <c r="I23" s="19"/>
@@ -2826,16 +2836,14 @@
       <c r="K23" s="19"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="2:12" s="51" customFormat="1" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B24" s="32"/>
       <c r="C24" s="14"/>
       <c r="D24" s="46" t="s">
         <v>72</v>
       </c>
       <c r="E24" s="19"/>
-      <c r="F24" s="29" t="s">
-        <v>99</v>
-      </c>
+      <c r="F24" s="25"/>
       <c r="G24" s="19"/>
       <c r="H24" s="45"/>
       <c r="I24" s="19"/>
@@ -2850,9 +2858,7 @@
         <v>101</v>
       </c>
       <c r="E25" s="19"/>
-      <c r="F25" s="34" t="s">
-        <v>17</v>
-      </c>
+      <c r="F25" s="25"/>
       <c r="G25" s="19"/>
       <c r="H25" s="45"/>
       <c r="I25" s="19"/>
@@ -2869,9 +2875,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="19"/>
-      <c r="F26" s="38" t="s">
-        <v>100</v>
-      </c>
+      <c r="F26" s="25"/>
       <c r="G26" s="19"/>
       <c r="H26" s="45"/>
       <c r="I26" s="19"/>
@@ -2886,7 +2890,7 @@
         <v>71</v>
       </c>
       <c r="E27" s="19"/>
-      <c r="F27" s="34"/>
+      <c r="F27" s="25"/>
       <c r="G27" s="19"/>
       <c r="H27" s="45"/>
       <c r="I27" s="19"/>
@@ -2894,14 +2898,12 @@
       <c r="K27" s="19"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="2:12" s="51" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B28" s="32"/>
       <c r="C28" s="14"/>
       <c r="D28" s="35"/>
       <c r="E28" s="19"/>
-      <c r="F28" s="82" t="s">
-        <v>24</v>
-      </c>
+      <c r="F28" s="25"/>
       <c r="G28" s="19"/>
       <c r="H28" s="45"/>
       <c r="I28" s="19"/>
@@ -3133,7 +3135,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -3794,7 +3796,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -4442,7 +4444,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -5178,7 +5180,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -5377,11 +5379,11 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C14" s="22"/>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="20"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="20"/>
       <c r="G14" s="19"/>
       <c r="H14" s="24" t="s">
         <v>11</v>
@@ -5396,11 +5398,11 @@
     <row r="15" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="20"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="20"/>
       <c r="G15" s="19"/>
       <c r="H15" s="29" t="s">
         <v>55</v>
@@ -5415,11 +5417,11 @@
     <row r="16" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B16" s="32"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="48" t="s">
-        <v>17</v>
-      </c>
+      <c r="D16" s="20"/>
       <c r="E16" s="28"/>
-      <c r="F16" s="20"/>
+      <c r="F16" s="48" t="s">
+        <v>17</v>
+      </c>
       <c r="G16" s="19"/>
       <c r="H16" s="34" t="s">
         <v>17</v>
@@ -5436,11 +5438,11 @@
         <v>0.5</v>
       </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="20"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="20"/>
       <c r="G17" s="19"/>
       <c r="H17" s="38" t="s">
         <v>56</v>
@@ -5455,9 +5457,9 @@
     <row r="18" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B18" s="41"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="49"/>
+      <c r="D18" s="20"/>
       <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
+      <c r="F18" s="49"/>
       <c r="G18" s="19"/>
       <c r="H18" s="34"/>
       <c r="I18" s="19"/>
@@ -5468,11 +5470,11 @@
     <row r="19" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B19" s="32"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="20"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="20"/>
       <c r="G19" s="19"/>
       <c r="H19" s="82" t="s">
         <v>32</v>
@@ -5850,7 +5852,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -6274,7 +6276,7 @@
       <c r="K27" s="19"/>
       <c r="L27" s="25"/>
     </row>
-    <row r="28" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" s="51" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="B28" s="32"/>
       <c r="C28" s="14"/>
       <c r="D28" s="20"/>
@@ -6282,7 +6284,7 @@
       <c r="F28" s="20"/>
       <c r="G28" s="19"/>
       <c r="H28" s="75" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="55"/>
@@ -6511,7 +6513,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -6873,9 +6875,13 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="C23" s="14"/>
-      <c r="D23" s="20"/>
+      <c r="D23" s="46" t="s">
+        <v>12</v>
+      </c>
       <c r="E23" s="19"/>
-      <c r="F23" s="45"/>
+      <c r="F23" s="46" t="s">
+        <v>12</v>
+      </c>
       <c r="G23" s="19"/>
       <c r="H23" s="74"/>
       <c r="I23" s="19"/>
@@ -6883,12 +6889,16 @@
       <c r="K23" s="19"/>
       <c r="L23" s="25"/>
     </row>
-    <row r="24" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" s="51" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="B24" s="32"/>
       <c r="C24" s="14"/>
-      <c r="D24" s="20"/>
+      <c r="D24" s="47" t="s">
+        <v>19</v>
+      </c>
       <c r="E24" s="19"/>
-      <c r="F24" s="45"/>
+      <c r="F24" s="30" t="s">
+        <v>45</v>
+      </c>
       <c r="G24" s="19"/>
       <c r="H24" s="45"/>
       <c r="I24" s="19"/>
@@ -6899,9 +6909,13 @@
     <row r="25" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B25" s="26"/>
       <c r="C25" s="14"/>
-      <c r="D25" s="20"/>
+      <c r="D25" s="48" t="s">
+        <v>17</v>
+      </c>
       <c r="E25" s="19"/>
-      <c r="F25" s="45"/>
+      <c r="F25" s="35" t="s">
+        <v>17</v>
+      </c>
       <c r="G25" s="19"/>
       <c r="H25" s="45"/>
       <c r="I25" s="19"/>
@@ -6914,12 +6928,12 @@
         <v>0.625</v>
       </c>
       <c r="C26" s="22"/>
-      <c r="D26" s="46" t="s">
-        <v>33</v>
+      <c r="D26" s="49" t="s">
+        <v>65</v>
       </c>
       <c r="E26" s="19"/>
-      <c r="F26" s="46" t="s">
-        <v>33</v>
+      <c r="F26" s="39" t="s">
+        <v>27</v>
       </c>
       <c r="G26" s="19"/>
       <c r="H26" s="46" t="s">
@@ -6933,13 +6947,9 @@
     <row r="27" spans="2:12" s="51" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="B27" s="32"/>
       <c r="C27" s="14"/>
-      <c r="D27" s="47" t="s">
-        <v>19</v>
-      </c>
+      <c r="D27" s="83"/>
       <c r="E27" s="19"/>
-      <c r="F27" s="30" t="s">
-        <v>45</v>
-      </c>
+      <c r="F27" s="35"/>
       <c r="G27" s="19"/>
       <c r="H27" s="78" t="s">
         <v>64</v>
@@ -6952,12 +6962,12 @@
     <row r="28" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B28" s="32"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="48" t="s">
-        <v>17</v>
+      <c r="D28" s="75" t="s">
+        <v>34</v>
       </c>
       <c r="E28" s="19"/>
-      <c r="F28" s="35" t="s">
-        <v>17</v>
+      <c r="F28" s="43" t="s">
+        <v>34</v>
       </c>
       <c r="G28" s="19"/>
       <c r="H28" s="79" t="s">
@@ -6973,13 +6983,9 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="C29" s="14"/>
-      <c r="D29" s="49" t="s">
-        <v>65</v>
-      </c>
+      <c r="D29" s="45"/>
       <c r="E29" s="19"/>
-      <c r="F29" s="39" t="s">
-        <v>27</v>
-      </c>
+      <c r="F29" s="45"/>
       <c r="G29" s="19"/>
       <c r="H29" s="80" t="s">
         <v>119</v>
@@ -6992,9 +6998,9 @@
     <row r="30" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B30" s="32"/>
       <c r="C30" s="19"/>
-      <c r="D30" s="83"/>
+      <c r="D30" s="45"/>
       <c r="E30" s="19"/>
-      <c r="F30" s="35"/>
+      <c r="F30" s="45"/>
       <c r="G30" s="19"/>
       <c r="H30" s="79"/>
       <c r="I30" s="19"/>
@@ -7005,13 +7011,9 @@
     <row r="31" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B31" s="32"/>
       <c r="C31" s="19"/>
-      <c r="D31" s="75" t="s">
-        <v>34</v>
-      </c>
+      <c r="D31" s="45"/>
       <c r="E31" s="19"/>
-      <c r="F31" s="43" t="s">
-        <v>34</v>
-      </c>
+      <c r="F31" s="45"/>
       <c r="G31" s="19"/>
       <c r="H31" s="81" t="s">
         <v>37</v>
@@ -7202,7 +7204,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -7873,7 +7875,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -8554,7 +8556,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -8865,11 +8867,11 @@
       </c>
       <c r="E19" s="19"/>
       <c r="F19" s="75" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="91" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="82" t="s">
@@ -9038,7 +9040,7 @@
       </c>
       <c r="I28" s="19"/>
       <c r="J28" s="91" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K28" s="19"/>
       <c r="L28" s="25"/>
@@ -9295,7 +9297,7 @@
       <c r="B4" s="77"/>
       <c r="C4" s="77"/>
       <c r="D4" s="105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" s="106"/>
       <c r="F4" s="106"/>
@@ -9478,7 +9480,9 @@
       <c r="E14" s="14"/>
       <c r="F14" s="20"/>
       <c r="G14" s="19"/>
-      <c r="H14" s="25"/>
+      <c r="H14" s="24" t="s">
+        <v>11</v>
+      </c>
       <c r="I14" s="14"/>
       <c r="J14" s="24" t="s">
         <v>11</v>
@@ -9493,7 +9497,9 @@
       <c r="E15" s="28"/>
       <c r="F15" s="20"/>
       <c r="G15" s="19"/>
-      <c r="H15" s="25"/>
+      <c r="H15" s="62" t="s">
+        <v>94</v>
+      </c>
       <c r="I15" s="19"/>
       <c r="J15" s="62" t="s">
         <v>94</v>
@@ -9508,7 +9514,9 @@
       <c r="E16" s="28"/>
       <c r="F16" s="20"/>
       <c r="G16" s="19"/>
-      <c r="H16" s="25"/>
+      <c r="H16" s="65" t="s">
+        <v>17</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="65" t="s">
         <v>17</v>
@@ -9525,7 +9533,9 @@
       <c r="E17" s="28"/>
       <c r="F17" s="20"/>
       <c r="G17" s="19"/>
-      <c r="H17" s="25"/>
+      <c r="H17" s="68" t="s">
+        <v>95</v>
+      </c>
       <c r="I17" s="19"/>
       <c r="J17" s="68" t="s">
         <v>95</v>
@@ -9540,7 +9550,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="19"/>
-      <c r="H18" s="25"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="19"/>
       <c r="J18" s="65"/>
       <c r="K18" s="19"/>
@@ -9553,7 +9563,9 @@
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
       <c r="G19" s="19"/>
-      <c r="H19" s="25"/>
+      <c r="H19" s="71" t="s">
+        <v>24</v>
+      </c>
       <c r="I19" s="19"/>
       <c r="J19" s="71" t="s">
         <v>24</v>

--- a/Orario.xlsx
+++ b/Orario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentiunical-my.sharepoint.com/personal/roberto_antonucci_servizimicrosoft_unical_it/Documents/Documenti/Documents/DOCUMENTI/Protocollo Informatico/Titolo 3/Titolo III.8/Programmazione Didattica 2026-2027/Orario 1 semestre/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{47FFEA90-37AE-410C-B2D2-9CE352867A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C1434F-C354-45CA-BCBB-F197073231B4}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{47FFEA90-37AE-410C-B2D2-9CE352867A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04217E3E-86ED-4387-BBB3-45B767D4E2A3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Economia I" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="126">
   <si>
     <t>Lunedì</t>
   </si>
@@ -4527,9 +4527,7 @@
         <v>0.375</v>
       </c>
       <c r="C8" s="22"/>
-      <c r="D8" s="24" t="s">
-        <v>10</v>
-      </c>
+      <c r="D8" s="74"/>
       <c r="E8" s="14"/>
       <c r="F8" s="74"/>
       <c r="G8" s="19"/>
@@ -4548,9 +4546,7 @@
     <row r="9" spans="2:18" s="51" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="B9" s="26"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="30" t="s">
-        <v>42</v>
-      </c>
+      <c r="D9" s="55"/>
       <c r="E9" s="28"/>
       <c r="F9" s="55"/>
       <c r="G9" s="19"/>
@@ -4569,9 +4565,7 @@
     <row r="10" spans="2:18" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B10" s="32"/>
       <c r="C10" s="14"/>
-      <c r="D10" s="35" t="s">
-        <v>17</v>
-      </c>
+      <c r="D10" s="55"/>
       <c r="E10" s="19"/>
       <c r="F10" s="55"/>
       <c r="G10" s="19"/>
@@ -4592,9 +4586,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="C11" s="14"/>
-      <c r="D11" s="39" t="s">
-        <v>115</v>
-      </c>
+      <c r="D11" s="55"/>
       <c r="E11" s="19"/>
       <c r="F11" s="55"/>
       <c r="G11" s="19"/>
@@ -4613,7 +4605,7 @@
     <row r="12" spans="2:18" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B12" s="41"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="35"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="19"/>
       <c r="F12" s="55"/>
       <c r="G12" s="19"/>
@@ -4626,9 +4618,7 @@
     <row r="13" spans="2:18" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B13" s="41"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="43" t="s">
-        <v>32</v>
-      </c>
+      <c r="D13" s="60"/>
       <c r="E13" s="19"/>
       <c r="F13" s="60"/>
       <c r="G13" s="19"/>
@@ -8074,9 +8064,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="C14" s="22"/>
-      <c r="D14" s="24" t="s">
-        <v>11</v>
-      </c>
+      <c r="D14" s="74"/>
       <c r="E14" s="14"/>
       <c r="F14" s="24" t="s">
         <v>11</v>
@@ -8095,9 +8083,7 @@
     <row r="15" spans="2:12" s="51" customFormat="1" ht="52.5" x14ac:dyDescent="0.25">
       <c r="B15" s="41"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="29" t="s">
-        <v>77</v>
-      </c>
+      <c r="D15" s="55"/>
       <c r="E15" s="28"/>
       <c r="F15" s="29" t="s">
         <v>77</v>
@@ -8116,9 +8102,7 @@
     <row r="16" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B16" s="32"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="34" t="s">
-        <v>17</v>
-      </c>
+      <c r="D16" s="55"/>
       <c r="E16" s="28"/>
       <c r="F16" s="34" t="s">
         <v>17</v>
@@ -8139,9 +8123,7 @@
         <v>0.5</v>
       </c>
       <c r="C17" s="14"/>
-      <c r="D17" s="38" t="s">
-        <v>78</v>
-      </c>
+      <c r="D17" s="55"/>
       <c r="E17" s="28"/>
       <c r="F17" s="38" t="s">
         <v>78</v>
@@ -8160,7 +8142,7 @@
     <row r="18" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B18" s="41"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="34"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="19"/>
       <c r="F18" s="34"/>
       <c r="G18" s="19"/>
@@ -8173,9 +8155,7 @@
     <row r="19" spans="2:12" s="51" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B19" s="32"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="82" t="s">
-        <v>28</v>
-      </c>
+      <c r="D19" s="20"/>
       <c r="E19" s="19"/>
       <c r="F19" s="82" t="s">
         <v>28</v>
